--- a/docs/기업프로필_템플릿.xlsx
+++ b/docs/기업프로필_템플릿.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>소재지(전남/광주/기타)</t>
+          <t>소재지(시·도)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -734,7 +734,7 @@
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"전남,광주,기타"</formula1>
+      <formula1>"서울,부산,대구,인천,광주,대전,울산,세종,경기,강원,충북,충남,전북,전남,경북,경남,제주"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"소기업·소상공인,중소기업,중견기업,대기업"</formula1>

--- a/docs/기업프로필_템플릿.xlsx
+++ b/docs/기업프로필_템플릿.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -438,7 +438,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -477,7 +477,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>업종(농산,수산,식품,공산품,기타)</t>
+          <t>업종(농수산,식품,화장품(뷰티),공예품,생활용품(소비재),의료기기,기타 공산품)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>수산,식품</t>
+          <t>농수산,식품</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>공산품</t>
+          <t>기타 공산품</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>농산,식품</t>
+          <t>농수산,식품</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -728,6 +728,76 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>통번역, 해외전시·박람회</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(예시) 목포뷰티</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>456-78-90123</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>소기업·소상공인</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>화장품(뷰티)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>기초화장품, 마스크팩</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3304.99</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>베트남, 중국</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>수출 초보(10만불 미만)</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>해외전시·박람회, 인증·규격</t>
         </is>
       </c>
     </row>
@@ -813,7 +883,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>농산, 수산, 식품, 공산품, 기타 중 해당 항목을 쉼표로 구분</t>
+          <t>농수산, 식품, 화장품(뷰티), 공예품, 생활용품(소비재), 의료기기, 기타 공산품 중 해당 항목을 쉼표로 구분 (여러 개 가능). 예전 값(농산·수산·공산품)도 자동 변환됩니다.</t>
         </is>
       </c>
     </row>
